--- a/output/stock_quant_scores/LMT_info.xlsx
+++ b/output/stock_quant_scores/LMT_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FU2"/>
+  <dimension ref="A1:GA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,375 +936,405 @@
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
+          <t>recommendationMean</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>numberOfAnalystOpinions</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>dividendDate</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>dividendDate</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FQ1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FR1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FS1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1430,28 +1460,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>486.67</v>
+        <v>484.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>487.15</v>
+        <v>487.91</v>
       </c>
       <c r="AE2" t="n">
-        <v>486.01</v>
+        <v>484.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>495.18</v>
+        <v>490.7499</v>
       </c>
       <c r="AG2" t="n">
-        <v>486.67</v>
+        <v>484.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>487.15</v>
+        <v>487.91</v>
       </c>
       <c r="AI2" t="n">
-        <v>486.01</v>
+        <v>484.57</v>
       </c>
       <c r="AJ2" t="n">
-        <v>495.18</v>
+        <v>490.7499</v>
       </c>
       <c r="AK2" t="n">
         <v>13.2</v>
@@ -1472,40 +1502,40 @@
         <v>0.262</v>
       </c>
       <c r="AQ2" t="n">
-        <v>27.311062</v>
+        <v>27.32287</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.303806</v>
+        <v>17.340448</v>
       </c>
       <c r="AS2" t="n">
-        <v>829066</v>
+        <v>759442</v>
       </c>
       <c r="AT2" t="n">
-        <v>829066</v>
+        <v>759440</v>
       </c>
       <c r="AU2" t="n">
-        <v>1659603</v>
+        <v>1638853</v>
       </c>
       <c r="AV2" t="n">
-        <v>1355450</v>
+        <v>1335760</v>
       </c>
       <c r="AW2" t="n">
-        <v>1355450</v>
+        <v>1335760</v>
       </c>
       <c r="AX2" t="n">
-        <v>487.16</v>
+        <v>487.58</v>
       </c>
       <c r="AY2" t="n">
-        <v>487.33</v>
+        <v>488.47</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>113559740416</v>
+        <v>113800208384</v>
       </c>
       <c r="BC2" t="n">
         <v>410.11</v>
@@ -1520,19 +1550,19 @@
         <v>0.281186</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.5806433</v>
+        <v>1.5839903</v>
       </c>
       <c r="BH2" t="n">
-        <v>447.9402</v>
+        <v>448.885</v>
       </c>
       <c r="BI2" t="n">
-        <v>463.2631</v>
+        <v>462.8132</v>
       </c>
       <c r="BJ2" t="n">
         <v>13.05</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.026814884</v>
+        <v>0.026943883</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1543,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>133965438976</v>
+        <v>134145204224</v>
       </c>
       <c r="BO2" t="n">
         <v>0.058520004</v>
@@ -1555,40 +1585,40 @@
         <v>233465056</v>
       </c>
       <c r="BR2" t="n">
-        <v>2089408</v>
+        <v>2459639</v>
       </c>
       <c r="BS2" t="n">
-        <v>3166167</v>
+        <v>2737007</v>
       </c>
       <c r="BT2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0105</v>
       </c>
       <c r="BW2" t="n">
         <v>0.00082</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.75583</v>
+        <v>0.75588</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0106</v>
+        <v>0.0125</v>
       </c>
       <c r="CA2" t="n">
-        <v>233465056</v>
+        <v>234385728</v>
       </c>
       <c r="CB2" t="n">
         <v>22.991</v>
       </c>
       <c r="CC2" t="n">
-        <v>21.15654</v>
+        <v>21.20134</v>
       </c>
       <c r="CD2" t="n">
         <v>1735603200</v>
@@ -1606,7 +1636,7 @@
         <v>4204000000</v>
       </c>
       <c r="CI2" t="n">
-        <v>17.81</v>
+        <v>17.84</v>
       </c>
       <c r="CJ2" t="n">
         <v>28.11</v>
@@ -1620,16 +1650,16 @@
         <v>915408000</v>
       </c>
       <c r="CM2" t="n">
-        <v>1.865</v>
+        <v>1.867</v>
       </c>
       <c r="CN2" t="n">
-        <v>18.622</v>
+        <v>18.647</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.15792298</v>
+        <v>-0.16614205</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CQ2" t="n">
         <v>3.3</v>
@@ -1643,7 +1673,7 @@
         </is>
       </c>
       <c r="CT2" t="n">
-        <v>486.41</v>
+        <v>487.44</v>
       </c>
       <c r="CU2" t="n">
         <v>544</v>
@@ -1652,277 +1682,297 @@
         <v>398</v>
       </c>
       <c r="CW2" t="n">
-        <v>479.55557</v>
+        <v>473.9412</v>
       </c>
       <c r="CX2" t="n">
-        <v>482</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CZ2" t="n">
-        <v>18</v>
+        <v>465</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>2.52632</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
       </c>
       <c r="DA2" t="n">
+        <v>17</v>
+      </c>
+      <c r="DB2" t="n">
         <v>1292999936</v>
       </c>
-      <c r="DB2" t="n">
+      <c r="DC2" t="n">
         <v>5.538</v>
       </c>
-      <c r="DC2" t="n">
+      <c r="DD2" t="n">
         <v>7193999872</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DE2" t="n">
         <v>21638000640</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DF2" t="n">
         <v>0.8</v>
       </c>
-      <c r="DF2" t="n">
+      <c r="DG2" t="n">
         <v>0.985</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DH2" t="n">
         <v>71844003840</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="DI2" t="n">
         <v>405.662</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DJ2" t="n">
         <v>305.2</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DK2" t="n">
         <v>0.06467000000000001</v>
       </c>
-      <c r="DK2" t="n">
+      <c r="DL2" t="n">
         <v>0.73056</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="DM2" t="n">
         <v>5929999872</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="DN2" t="n">
         <v>3821625088</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="DO2" t="n">
         <v>5071000064</v>
       </c>
-      <c r="DO2" t="n">
+      <c r="DP2" t="n">
         <v>-0.787</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DQ2" t="n">
         <v>0.002</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DR2" t="n">
         <v>0.08254</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="DS2" t="n">
         <v>0.10012999</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="DT2" t="n">
         <v>0.038829997</v>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>LMT</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>Nasdaq Real Time Price</t>
         </is>
       </c>
-      <c r="DZ2" t="b">
+      <c r="EA2" t="b">
         <v>1</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
       <c r="EC2" t="inlineStr">
         <is>
+          <t>NYQ</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>finmb_285827</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="EG2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0.640048</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>487.44</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EN2" t="n">
+        <v>1758931197</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1638853</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>77.33002</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>0.18855922</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>410.11 - 618.95</t>
+        </is>
+      </c>
+      <c r="ET2" t="n">
+        <v>-131.51001</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>-0.21247275</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-16.614204</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1758844800</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1753187400</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1761049800</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1761049800</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1753196400</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1753196400</v>
+      </c>
+      <c r="FC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>21.9249</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>22.232256</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>38.554993</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>0.085890576</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>24.6268</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>0.0532111</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
+          <t>2.5 - Hold</t>
+        </is>
+      </c>
+      <c r="FO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>-252322200000</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>0.084113665</v>
+      </c>
+      <c r="FS2" t="n">
+        <v>487.85</v>
+      </c>
+      <c r="FT2" t="n">
+        <v>0.41000366</v>
+      </c>
+      <c r="FU2" t="n">
+        <v>3.10001</v>
+      </c>
+      <c r="FV2" t="inlineStr">
+        <is>
+          <t>484.57 - 490.7499</t>
+        </is>
+      </c>
+      <c r="FW2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="FX2" t="inlineStr">
+        <is>
           <t>Lockheed Martin Corporation</t>
         </is>
       </c>
-      <c r="ED2" t="inlineStr">
+      <c r="FY2" t="inlineStr">
         <is>
           <t>Lockheed Martin Corporation</t>
         </is>
       </c>
-      <c r="EE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-252322200000</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.26000977</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>486.01 - 495.18</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1659603</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>NYQ</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>finmb_285827</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="EQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>1758740029</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.053426296</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>486.41</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>76.30002</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>0.1860477</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>410.11 - 618.95</t>
-        </is>
-      </c>
-      <c r="EY2" t="n">
-        <v>-132.54001</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>-0.21413685</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>-15.792298</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1758844800</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>1753187400</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1761049800</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>1761049800</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>1753196400</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>1753196400</v>
-      </c>
-      <c r="FH2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>17.81</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>21.9249</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>22.185278</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>38.46982</v>
-      </c>
-      <c r="FN2" t="n">
-        <v>0.0858816</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>23.146912</v>
-      </c>
-      <c r="FP2" t="n">
-        <v>0.04996494</v>
-      </c>
-      <c r="FQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FT2" t="inlineStr">
+      <c r="FZ2" t="inlineStr">
         <is>
           <t>Lockheed Martin</t>
         </is>
       </c>
-      <c r="FU2" t="n">
-        <v>1.6175</v>
+      <c r="GA2" t="n">
+        <v>1.6201</v>
       </c>
     </row>
   </sheetData>
